--- a/errors_warnings.xlsx
+++ b/errors_warnings.xlsx
@@ -19,18 +19,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>E1-1</t>
   </si>
   <si>
-    <t>Unable to cancel the pending deletion of an AutoDelObj</t>
-  </si>
-  <si>
     <t>Errors</t>
   </si>
   <si>
     <t>Warnings</t>
+  </si>
+  <si>
+    <t>Unable to unschedule the pending deletion of a member object of an SDelPool object.</t>
+  </si>
+  <si>
+    <t>E1-2</t>
+  </si>
+  <si>
+    <t>Unable to dispatch user input.</t>
+  </si>
+  <si>
+    <t>E</t>
   </si>
 </sst>
 </file>
@@ -405,7 +414,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:F3"/>
+  <dimension ref="A2:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
@@ -417,20 +426,33 @@
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3"/>
       <c r="E2" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" s="4"/>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
